--- a/data/trans_camb/IP42B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 40,95</t>
+          <t>-5,29; 43,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 16,41</t>
+          <t>-18,02; 16,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,54; 61,21</t>
+          <t>13,06; 62,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 25,95</t>
+          <t>-6,21; 25,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 44,42</t>
+          <t>11,41; 45,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 17,88</t>
+          <t>-7,02; 16,87</t>
         </is>
       </c>
     </row>
@@ -727,19 +727,19 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,68; —</t>
+          <t>29,44; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,89; —</t>
+          <t>-67,33; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 14,01</t>
+          <t>-17,96; 15,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 12,43</t>
+          <t>-19,39; 11,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 22,42</t>
+          <t>0,92; 22,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 13,28</t>
+          <t>-4,13; 13,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 15,67</t>
+          <t>-2,22; 16,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 9,72</t>
+          <t>-7,61; 10,57</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 293,87</t>
+          <t>-66,35; 308,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,69; 272,47</t>
+          <t>-77,13; 278,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,19 +883,19 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 532,52</t>
+          <t>-23,98; 578,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 272,85</t>
+          <t>-55,02; 355,87</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 4,17</t>
+          <t>-22,82; 7,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 7,75</t>
+          <t>-26,05; 4,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,96</t>
+          <t>0,0; 29,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,89</t>
+          <t>0,0; 13,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 13,43</t>
+          <t>-3,61; 13,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 5,48</t>
+          <t>-7,13; 6,13</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 29,82</t>
+          <t>-17,01; 30,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 5,53</t>
+          <t>-33,15; 3,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 7,04</t>
+          <t>-11,36; 7,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 22,28</t>
+          <t>-2,37; 23,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 16,04</t>
+          <t>-8,65; 17,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 10,83</t>
+          <t>-12,22; 10,34</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,1; 670,01</t>
+          <t>-65,59; 692,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 433,72</t>
+          <t>-62,61; 564,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 389,93</t>
+          <t>-78,13; 371,61</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 45,47</t>
+          <t>-43,07; 45,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 8,74</t>
+          <t>-59,47; 8,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,07</t>
+          <t>0,0; 37,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,49</t>
+          <t>0,0; 18,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 34,62</t>
+          <t>-7,94; 34,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 5,52</t>
+          <t>-30,98; 5,49</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 23,42</t>
+          <t>-14,15; 26,19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 11,39</t>
+          <t>-17,78; 11,49</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,74; 28,81</t>
+          <t>2,85; 27,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,8</t>
+          <t>0,0; 42,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 18,4</t>
+          <t>-3,79; 17,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 18,92</t>
+          <t>-5,05; 17,83</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,79; 989,52</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,15; 31,17</t>
+          <t>3,87; 28,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 16,61</t>
+          <t>-3,5; 16,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 21,8</t>
+          <t>-7,31; 22,77</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 0,0</t>
+          <t>-23,72; -1,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,58; 21,95</t>
+          <t>2,11; 22,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 3,98</t>
+          <t>-10,17; 4,62</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>4,97; —</t>
+          <t>-3,15; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-77,47; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 318,46</t>
+          <t>-42,86; 326,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,56</t>
+          <t>-100,0; 21,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,92; 465,85</t>
+          <t>9,91; 493,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 90,34</t>
+          <t>-73,58; 103,78</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 8,2</t>
+          <t>-11,58; 8,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 12,03</t>
+          <t>-8,6; 11,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -1,48</t>
+          <t>-30,0; -1,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-27,89; -1,57</t>
+          <t>-28,81; -0,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 0,65</t>
+          <t>-17,28; 0,7</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 2,82</t>
+          <t>-16,98; 1,28</t>
         </is>
       </c>
     </row>
@@ -1804,27 +1804,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-76,89; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-92,46; 23,14</t>
+          <t>-93,22; 0,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-92,46; 11,35</t>
+          <t>-90,13; 51,97</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-84,9; 25,17</t>
+          <t>-84,53; 32,34</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-76,5; 48,94</t>
+          <t>-78,93; 27,59</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,94</t>
+          <t>0,77; 12,58</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,78</t>
+          <t>-5,82; 4,45</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,05; 12,01</t>
+          <t>1,41; 12,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 4,26</t>
+          <t>-4,3; 4,65</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,42</t>
+          <t>2,82; 10,81</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,09</t>
+          <t>-3,69; 3,22</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3,9; 202,66</t>
+          <t>5,64; 216,23</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 61,13</t>
+          <t>-46,56; 78,74</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5,6; 221,98</t>
+          <t>9,34; 232,08</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 85,14</t>
+          <t>-41,96; 104,87</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>20,3; 168,19</t>
+          <t>27,35; 163,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 49,73</t>
+          <t>-35,4; 49,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 43,04</t>
+          <t>-6,92; 40,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 16,22</t>
+          <t>-20,75; 17,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 62,53</t>
+          <t>13,11; 62,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 25,25</t>
+          <t>-7,78; 25,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,41; 45,16</t>
+          <t>11,33; 45,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 16,87</t>
+          <t>-5,19; 17,36</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,44; —</t>
+          <t>44,29; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,33; —</t>
+          <t>-62,69; —</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 15,47</t>
+          <t>-19,7; 14,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 11,89</t>
+          <t>-23,29; 12,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 22,68</t>
+          <t>0,16; 23,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 13,45</t>
+          <t>-5,57; 14,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 16,8</t>
+          <t>-4,75; 15,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 10,57</t>
+          <t>-8,81; 9,37</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-66,35; 308,11</t>
+          <t>-73,23; 260,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 278,0</t>
+          <t>-76,57; 315,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 578,03</t>
+          <t>-40,58; 409,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,02; 355,87</t>
+          <t>-58,58; 257,3</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 7,95</t>
+          <t>-22,51; 7,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 4,36</t>
+          <t>-24,47; 4,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,33</t>
+          <t>0,0; 29,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,33</t>
+          <t>0,0; 13,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 13,82</t>
+          <t>-4,29; 12,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 6,13</t>
+          <t>-7,52; 5,24</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 30,84</t>
+          <t>-14,53; 30,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 3,54</t>
+          <t>-30,75; 4,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 7,15</t>
+          <t>-11,29; 7,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 23,52</t>
+          <t>-2,39; 22,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 17,91</t>
+          <t>-8,52; 16,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 10,34</t>
+          <t>-13,37; 10,52</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,59; 692,67</t>
+          <t>-64,31; 755,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,61; 564,39</t>
+          <t>-66,84; 600,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,13; 371,61</t>
+          <t>-83,89; 335,97</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 45,07</t>
+          <t>-49,95; 46,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 8,57</t>
+          <t>-59,68; 8,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,88</t>
+          <t>0,0; 37,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,54</t>
+          <t>0,0; 15,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 34,82</t>
+          <t>-7,3; 33,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 5,49</t>
+          <t>-29,01; 5,44</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 26,19</t>
+          <t>-14,87; 25,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 11,49</t>
+          <t>-17,78; 11,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,85; 27,8</t>
+          <t>2,85; 28,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,25</t>
+          <t>0,0; 42,75</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 17,06</t>
+          <t>-3,89; 19,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 17,83</t>
+          <t>-5,29; 18,66</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-68,79; 989,52</t>
+          <t>-65,31; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,87; 28,35</t>
+          <t>3,91; 28,75</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 16,77</t>
+          <t>-3,03; 16,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 22,77</t>
+          <t>-8,92; 21,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -1,06</t>
+          <t>-22,17; 0,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,11; 22,61</t>
+          <t>2,47; 21,79</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 4,62</t>
+          <t>-11,01; 4,54</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,15; —</t>
+          <t>-7,76; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 326,78</t>
+          <t>-43,66; 315,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,18</t>
+          <t>-100,0; 39,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,91; 493,32</t>
+          <t>9,69; 481,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-73,58; 103,78</t>
+          <t>-77,78; 106,15</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 8,24</t>
+          <t>-12,18; 7,49</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 11,4</t>
+          <t>-9,93; 11,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -1,77</t>
+          <t>-29,62; -1,14</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-28,81; -0,39</t>
+          <t>-31,4; -1,87</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 0,7</t>
+          <t>-17,29; 0,71</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 1,28</t>
+          <t>-16,38; 1,63</t>
         </is>
       </c>
     </row>
@@ -1804,27 +1804,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,53; —</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-93,22; 0,82</t>
+          <t>-93,19; 27,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-90,13; 51,97</t>
+          <t>-92,84; 1,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-84,53; 32,34</t>
+          <t>-84,26; 26,76</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-78,93; 27,59</t>
+          <t>-75,81; 31,51</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,77; 12,58</t>
+          <t>0,43; 12,48</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,45</t>
+          <t>-5,84; 4,53</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,11</t>
+          <t>1,31; 12,76</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,65</t>
+          <t>-4,39; 4,38</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,81</t>
+          <t>2,55; 10,68</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,22</t>
+          <t>-4,04; 2,78</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5,64; 216,23</t>
+          <t>1,69; 193,66</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 78,74</t>
+          <t>-48,64; 80,72</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9,34; 232,08</t>
+          <t>10,13; 241,51</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 104,87</t>
+          <t>-43,95; 93,75</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>27,35; 163,49</t>
+          <t>24,33; 172,16</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 49,55</t>
+          <t>-38,64; 44,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>17,77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2,93</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 40,11</t>
+          <t>11,54; 61,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 17,06</t>
+          <t>-6,41; 25,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,11; 62,37</t>
+          <t>-7,89; 40,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 25,76</t>
+          <t>-18,01; 16,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 45,76</t>
+          <t>10,59; 44,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 17,36</t>
+          <t>-4,28; 17,88</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>755,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>191,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>252,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>41,75%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>755,35%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>191,26%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,29; —</t>
+          <t>47,68; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,69; —</t>
+          <t>-63,89; —</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,11</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-2,35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,8</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 14,04</t>
+          <t>-0,87; 22,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 12,63</t>
+          <t>-4,43; 13,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 23,51</t>
+          <t>-19,87; 14,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 14,4</t>
+          <t>-20,2; 12,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 15,18</t>
+          <t>-4,33; 15,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 9,37</t>
+          <t>-8,33; 9,72</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>391,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>169,67%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-0,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-15,07%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>391,79%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>169,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 260,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,57; 315,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,49; 293,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,69; 272,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 409,21</t>
+          <t>-33,93; 532,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 257,3</t>
+          <t>-58,1; 272,85</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,63</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-4,82</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-4,71</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 7,82</t>
+          <t>0,0; 29,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 4,35</t>
+          <t>0,0; 11,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,37</t>
+          <t>-26,3; 4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,26</t>
+          <t>-23,8; 7,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 12,94</t>
+          <t>-4,64; 13,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 5,24</t>
+          <t>-7,26; 5,48</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-54,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-53,01%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,62</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>8,73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-10,69</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 30,33</t>
+          <t>-12,73; 7,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 4,96</t>
+          <t>-1,33; 22,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 7,11</t>
+          <t>-17,18; 29,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 22,88</t>
+          <t>-31,01; 5,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 16,37</t>
+          <t>-9,93; 16,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 10,52</t>
+          <t>-10,73; 10,83</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-8,65%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>263,27%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>53,62%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-65,71%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-8,65%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>263,27%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 755,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-69,1; 670,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-66,84; 600,34</t>
+          <t>-62,56; 433,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,89; 335,97</t>
+          <t>-73,84; 389,93</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,01</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>11,98</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-14,3</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9,72</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,01</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-49,95; 46,08</t>
+          <t>0,0; 45,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 8,81</t>
+          <t>0,0; 15,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,86</t>
+          <t>-41,36; 45,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,2</t>
+          <t>-59,47; 8,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 33,43</t>
+          <t>-10,28; 34,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 5,44</t>
+          <t>-30,56; 5,52</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>64,11%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-76,53%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>10,46</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13,9</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>1,92</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-4,81</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>10,46</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>13,9</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 25,96</t>
+          <t>2,74; 28,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 11,59</t>
+          <t>0,0; 36,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,85; 28,77</t>
+          <t>-13,11; 23,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,75</t>
+          <t>-18,27; 11,39</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 19,39</t>
+          <t>-3,67; 18,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 18,66</t>
+          <t>-4,9; 18,92</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-49,3%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-65,31; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>7,86</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-9,96</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>16,11</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>5,75</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>7,86</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-9,96</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,91; 28,75</t>
+          <t>-7,32; 21,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 16,33</t>
+          <t>-22,94; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 21,19</t>
+          <t>5,15; 31,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 0,34</t>
+          <t>-4,69; 16,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,47; 21,79</t>
+          <t>2,58; 21,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 4,54</t>
+          <t>-10,63; 3,98</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>55,2%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-69,96%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>368,84%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>131,57%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>55,2%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-69,96%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,76; —</t>
+          <t>-37,02; 318,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 75,56</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-43,66; 315,8</t>
+          <t>4,97; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,99</t>
+          <t>-77,47; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,69; 481,94</t>
+          <t>14,92; 465,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,78; 106,15</t>
+          <t>-74,33; 90,34</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-13,9</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-13,75</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,55</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>2,65</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-13,9</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-13,75</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 7,49</t>
+          <t>-28,44; -1,48</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 11,14</t>
+          <t>-27,89; -1,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-29,62; -1,14</t>
+          <t>-11,78; 8,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-31,4; -1,87</t>
+          <t>-8,32; 12,03</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 0,71</t>
+          <t>-18,15; 0,65</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 1,63</t>
+          <t>-15,93; 2,82</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-68,78%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-68,03%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-9,23%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>44,59%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-68,78%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-68,03%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-92,46; 23,14</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-87,53; —</t>
+          <t>-92,46; 11,35</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-93,19; 27,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-92,84; 1,54</t>
+          <t>-76,89; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-84,26; 26,76</t>
+          <t>-84,9; 25,17</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,81; 31,51</t>
+          <t>-76,5; 48,94</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>6,72</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>6,61</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,76</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,43; 12,48</t>
+          <t>1,05; 12,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 4,53</t>
+          <t>-4,21; 4,26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,76</t>
+          <t>0,68; 12,94</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,38</t>
+          <t>-5,97; 3,78</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,68</t>
+          <t>2,55; 10,42</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,78</t>
+          <t>-3,99; 3,09</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>71,93%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-8,26%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>1,69; 193,66</t>
+          <t>5,6; 221,98</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 80,72</t>
+          <t>-43,68; 85,14</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10,13; 241,51</t>
+          <t>3,9; 202,66</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 93,75</t>
+          <t>-50,08; 61,13</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>24,33; 172,16</t>
+          <t>20,3; 168,19</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 44,13</t>
+          <t>-38,31; 49,73</t>
         </is>
       </c>
     </row>
